--- a/operation_data.xlsx
+++ b/operation_data.xlsx
@@ -826,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1015,6 +1015,76 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Comprobante Interno (No Fiscal)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>COMPROBANTE-INTERNO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>56-51561651-6</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Facturación Directa</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>PENDIENTE MEDIO DE PAGO</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1026,7 +1096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1212,6 +1282,76 @@
       <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Comprobante Interno (No Fiscal)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>COMPROBANTE-INTERNO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>56-51561651-6</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Facturación Directa</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>PENDIENTE MEDIO DE PAGO</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
         </is>
       </c>
     </row>
@@ -2053,15 +2193,11 @@
           <t>Caja Chica</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2102,15 +2238,11 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2151,15 +2283,11 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2200,15 +2328,11 @@
           <t>Transferencia - Banco Cordoba</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2249,15 +2373,11 @@
           <t>Transferencia - Banco Cordoba</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3994,7 +4114,11 @@
           <t>Banco</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Banco: Bancor | Cta: CC $ 331 0001176401 | CBU: 0200331101000001176415 | ALIAS: ECONCATIVO | Titular: Econcativo S.a.s (30719544009)</t>
+        </is>
+      </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
@@ -4006,7 +4130,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Cuenta Bancaria Principal Bancor</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4024,7 +4152,6 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>0</v>
       </c>
@@ -4058,14 +4185,12 @@
           <t>Cheques</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Sincronizado automáticamente con Cartera Cheques</t>
@@ -4148,7 +4273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4198,22 +4323,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>USR-000001</t>
+          <t>USR-000002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ailen Avalle</t>
+          <t>Lisandro Grangetto</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ailen Avalle</t>
+          <t>lichi.grangetto</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$Op9oTh036zgAAMcE$3be0513d6321c902fb5529e0ea6513f60147ac66e5553ef8a9f521889b2d7571b8a22a004d4adcde09f95eb626240158943c54c37005e3e155e8ba5d2e1f1940</t>
+          <t>scrypt:32768:8:1$d9QwZc5zitKbnPPb$8ab2692f2fea50f08ee44f5559a6fce51147eca48fa4b8745cfa9ef974dfc4605b8c38971196ee1a438e5fb2133701ea41844fbdb0b161bb612d15532146f368</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4228,29 +4353,29 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>USR-000002</t>
+          <t>USR-000003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lisandro Grangetto</t>
+          <t>Avalle Ailen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lichi.grangetto</t>
+          <t>Avalle.ailen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$d9QwZc5zitKbnPPb$8ab2692f2fea50f08ee44f5559a6fce51147eca48fa4b8745cfa9ef974dfc4605b8c38971196ee1a438e5fb2133701ea41844fbdb0b161bb612d15532146f368</t>
+          <t>scrypt:32768:8:1$W32g5gZAVPQGiVSQ$f32f8e855765d5c27454842fbd041b0902677291683440df71608338ffdc5be29f70e556b2259327ed16b40acb21e3bd87f0abb50c91fb2e5be2382ef88b0e7b</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4263,7 +4388,48 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>USR-000001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ailen Avalle</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ailen Avalle</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$rEh9KiKJbs4LgfYc$936c062e2a6a4806534e0015488307681ba70b4ebf64bf6193ccb690a5a1ecbdee3c830cd844b84339be64925ae643774bdad83bd27733bcb2ea989e27bb735b</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>07/10/2026 16:55</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4276,7 +4442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4354,6 +4520,53 @@
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CLI-000001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>56-51561651-6</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Municipalidad</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Exento / Estado</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>65456456456561</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hadesamp@gmail.com</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>safjkahbjds 654</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Activo</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4705,6 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4508,8 +4720,6 @@
           <t>2027-06-25</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4542,7 +4752,6 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4558,8 +4767,6 @@
           <t>2027-07-08</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4592,7 +4799,6 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4608,8 +4814,6 @@
           <t>2027-10-21</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4642,7 +4846,6 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4658,8 +4861,6 @@
           <t>2027-07-08</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4692,7 +4893,6 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4708,8 +4908,6 @@
           <t>2027-05-05</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4722,7 +4920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK4"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4965,6 +5163,603 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EMP-000001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Emanuel Roman Colazo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>36479383</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1992-06-11</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Soltero</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Malvinas Argentinas S/N</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Impira</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Impira</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3572507988</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>colazoema@gmail.com</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Cindy Daiana Soria</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Concubina</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Malvinas Argentinas S/N</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Impira</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3572528771</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Astropay</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Emanuel Colazo</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0000177507754010201407</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>PETAK.2026</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Chofer de Camión</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Completa</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Transferencia Bancaria</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>E.2, B.2</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>[{"tipo": "E.2", "vencimiento": "2026-10-27"}, {"tipo": "B.2", "vencimiento": "2027-05-26"}]</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EMP-000002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Omar Ramon Perotti</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>21404440</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1970-04-24</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Casado</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomas Garzon 235</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>zona 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Oncativo</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>omarperotti11@gmail.com</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Ines Liliana Peralta</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Esposa</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Tomas Garzon 235</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Oncativo</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3572506012</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Banco Macro</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Omar Perotti</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2850400540094100915328</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Chofer de Camión</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Completa</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Transferencia Bancaria</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>E.1</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2030-06-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EMP-000003</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pablo Alejandro Longhi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>32889429</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1987-06-22</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Casado</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Soldado Trillini 450</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>zona 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Oncativo</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Longpab22@gmail.com</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Lorena Moreyra</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Esposa</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Soldado Trillini 450</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Oncativo</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3572592357</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Mercado pago</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Pablo Longhi</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0000003100065094707200</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>PABLOL.2026</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Chofer de Camión</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Completa</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Transferencia Bancaria</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>E.1</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2027-04-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EMP-000004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Gomez Sergio Alejandro</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>24242660</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1974-10-15</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Soltero</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Zona Rural 1km de Ruta 9</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Oliva</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Oliva</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3532407452</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>MoniiPereyra79@gmail.com</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Monica Pereyra</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Concubina</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Zona Rural</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Oliva</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3532407631</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Mercado Pago</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Monica Pereyra</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0000003100037300736320</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>MONICA.451.CEIBO.MP</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Operador de Maquinaria</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Completa</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Transferencia Bancaria</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>E.1</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5090,14 +5885,11 @@
           <t>Grupo Margaria</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Combustible</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5106,14 +5898,11 @@
       <c r="I5" t="n">
         <v>-11050.5</v>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5131,7 +5920,6 @@
           <t>YPF</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Combustible</t>
@@ -5142,7 +5930,6 @@
           <t>3572505350</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5151,14 +5938,11 @@
       <c r="I6" t="n">
         <v>2304571.93</v>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5176,14 +5960,11 @@
           <t>Shell</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Combustible</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5192,7 +5973,6 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5203,7 +5983,6 @@
           <t>Saldo inicial pendiente de confirmar</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5236,7 +6015,6 @@
           <t>3572617398</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5245,13 +6023,11 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>CESOPOL.CORDOBA</t>
@@ -5302,13 +6078,11 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>0000003100008888777766 / YPF.DIRECTO.ONCATIVO</t>
@@ -5346,7 +6120,6 @@
           <t>+54 9 3584 86-6858 (ANAHI)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5355,13 +6128,11 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>2850400530094013288211</t>
@@ -5399,7 +6170,6 @@
           <t>+54 9 3572 50-0004</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5408,13 +6178,11 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>TACHA.BOLDO.POLLO</t>
@@ -5465,7 +6233,6 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5476,7 +6243,6 @@
           <t>Contacto: Alarcon Marina Maricel</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5494,7 +6260,6 @@
           <t>GOMERIA EL ALERO</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Repuestos</t>
@@ -5518,7 +6283,6 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5529,7 +6293,6 @@
           <t>Contacto: Lorena Fernandez</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5562,7 +6325,6 @@
           <t>+54 9 3572 55-0562</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5571,13 +6333,11 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>cbaceros</t>
@@ -5615,7 +6375,6 @@
           <t>35715322581</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5624,13 +6383,11 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>0200917301000000455283</t>
@@ -5668,7 +6425,6 @@
           <t>3572607034</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5677,14 +6433,11 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5717,7 +6470,6 @@
           <t>3572612848</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5726,13 +6478,11 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>levissamacro</t>
@@ -5770,7 +6520,6 @@
           <t>3572612848</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5779,13 +6528,11 @@
       <c r="I18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>lewissrlmacro</t>
@@ -5823,7 +6570,6 @@
           <t>3535107942</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5832,13 +6578,11 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>AMERICAGIS.BN</t>
@@ -5876,7 +6620,6 @@
           <t>3572593304</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5885,13 +6628,11 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>casagonella</t>
@@ -5929,7 +6670,6 @@
           <t>3572509148</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5938,13 +6678,11 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>VENUS.ANCHO.QUESO</t>
@@ -5967,7 +6705,6 @@
           <t>ADMINISTRACION PUMA</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Combustible</t>
@@ -5978,7 +6715,6 @@
           <t>3572446460</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -5987,14 +6723,11 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6022,8 +6755,6 @@
           <t>Servicios</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -6032,13 +6763,11 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>CCRAVEROZ</t>
@@ -6076,7 +6805,6 @@
           <t>3572677660</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -6085,13 +6813,11 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>JALCER.PINTURERIA</t>
@@ -6124,8 +6850,6 @@
           <t>Repuestos</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -6134,13 +6858,11 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>DOCTAREP</t>
@@ -6173,8 +6895,6 @@
           <t>Repuestos</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -6183,7 +6903,6 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>Activo</t>

--- a/operation_data.xlsx
+++ b/operation_data.xlsx
@@ -1096,7 +1096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1282,76 +1283,6 @@
       <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ING-000001</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Comprobante Interno (No Fiscal)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>COMPROBANTE-INTERNO</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>municipalidad de Oncativo</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>56-51561651-6</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Facturación Directa</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>100000</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>PENDIENTE MEDIO DE PAGO</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>100000</v>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Factura creada directamente</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4391,43 +4322,6 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>2026-10-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>USR-000001</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ailen Avalle</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ailen Avalle</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$rEh9KiKJbs4LgfYc$936c062e2a6a4806534e0015488307681ba70b4ebf64bf6193ccb690a5a1ecbdee3c830cd844b84339be64925ae643774bdad83bd27733bcb2ea989e27bb735b</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Administrador</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>07/10/2026 16:55</t>
         </is>
       </c>
     </row>

--- a/operation_data.xlsx
+++ b/operation_data.xlsx
@@ -826,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1023,32 +1023,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Comprobante Interno (No Fiscal)</t>
+          <t>Factura A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>00001</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>COMPROBANTE-INTERNO</t>
+          <t>00001-00000002</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>municipalidad de Oncativo</t>
+          <t>Municipalidad de Carrilobo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>56-51561651-6</t>
+          <t>30-99901691-6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>100000</v>
+        <v>5000000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1066,20 +1066,120 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>100000</v>
+        <v>5000000</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>PENDIENTE MEDIO DE PAGO</t>
+          <t>COBRADO</t>
         </is>
       </c>
       <c r="R5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Cheque: $1,000,000.00 - Caja Chica Efectivo</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="n">
-        <v>100000</v>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>REC-000001</t>
+        </is>
       </c>
       <c r="AB5" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ING-000002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Facturación Directa</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Transferencia: $2,000,000.00 | Cheque Físico (N° test1, test): $1,000,000.00 | E-Cheq (N° test2, test2): $1,000,000.00 | Cheque Físico (N° test3, test3): $1,000,000.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>REC-000002</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Factura creada directamente</t>
         </is>
@@ -1096,7 +1196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1143,7 +1243,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1283,6 +1382,91 @@
       <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>00001-00000002</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Facturación Directa</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Cheque: $1,000,000.00 - Caja Chica Efectivo</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>REC-000001</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1594,6 +1778,331 @@
       <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CHQ-000001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cheque Físico</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>bancor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>38485564</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ECONCATIVO S.A.S.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CHQ-000002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cheque Físico</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bancor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>38485565</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ECONCATIVO S.A.S.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CHQ-000003</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cheque Físico</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bancor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>38485566</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ECONCATIVO S.A.S.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CHQ-000004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cheque Físico</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bancor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>38485568</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ECONCATIVO S.A.S.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CHQ-000005</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cheque Físico</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bancor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>38485568</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ECONCATIVO S.A.S.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo</t>
         </is>
       </c>
     </row>
@@ -3970,7 +4479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4070,17 +4579,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CTA-001</t>
+          <t>CTA-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caja Chica Efectivo</t>
+          <t>Cartera de Cheques</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Cheques</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4089,40 +4598,7 @@
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>Caja Chica para Gastos Minoristas</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CTA-005</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cartera de Cheques</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Cheques</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
         <is>
           <t>Sincronizado automáticamente con Cartera Cheques</t>
         </is>
@@ -4284,7 +4760,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4797,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4420,17 +4896,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CLI-000001</t>
+          <t>CLI-000002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>municipalidad de Oncativo</t>
+          <t>Municipalidad de Oncativo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56-51561651-6</t>
+          <t>30-99901691-6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4443,22 +4919,44 @@
           <t>Exento / Estado</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>65456456456561</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>hadesamp@gmail.com</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>safjkahbjds 654</t>
+          <t>Bulnes 727</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CLI-000003</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>30-99922610-4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Municipalidad</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Exento / Estado</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/operation_data.xlsx
+++ b/operation_data.xlsx
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TEST</t>
+          <t>2312312312</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1151,33 +1151,18 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>COBRADO</t>
+          <t>PENDIENTE MEDIO DE PAGO</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Transferencia: $2,000,000.00 | Cheque Físico (N° test1, test): $1,000,000.00 | E-Cheq (N° test2, test2): $1,000,000.00 | Cheque Físico (N° test3, test3): $1,000,000.00 - Banco Cordoba</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>REC-000002</t>
-        </is>
+        <v>1000000</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -4680,7 +4665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4797,7 +4782,44 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>USR-000001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ailen Avalle</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ailen Avalle</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$wagVsgMFwai9CW1o$16a67cee9ae9a25c26a43d75c2fb07af7a8beb682a21454e6f01c80bbf7abdff7e152de3300a56904332e11dda9ba483fbfc7a68661da9d54a35fa7c3991cd48</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>14/10/2026 21:20</t>
         </is>
       </c>
     </row>

--- a/operation_data.xlsx
+++ b/operation_data.xlsx
@@ -826,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1015,161 +1015,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ING-000001</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Factura A</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00001</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>00001-00000002</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Municipalidad de Carrilobo</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>30-99901691-6</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Facturación Directa</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>COBRADO</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Cheque: $1,000,000.00 - Caja Chica Efectivo</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>REC-000001</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Factura creada directamente</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ING-000002</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Factura A</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2312312312</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Municipalidad de Oncativo</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>30-99901691-6</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Facturación Directa</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>PENDIENTE MEDIO DE PAGO</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Factura creada directamente</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1181,7 +1026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1367,91 +1212,6 @@
       <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ING-000001</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Factura A</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>00001</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>00001-00000002</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Municipalidad de Carrilobo</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>30-99901691-6</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Facturación Directa</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>COBRADO</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Cheque: $1,000,000.00 - Caja Chica Efectivo</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>REC-000001</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Factura creada directamente</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1557,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>bancor</t>
+          <t>Bancor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1820,14 +1580,9 @@
           <t>Disponible</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>ING-000001</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo</t>
+          <t>Cheque en cartera - Municipalidad de Carrilobo</t>
         </is>
       </c>
     </row>
@@ -1885,14 +1640,9 @@
           <t>Disponible</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>ING-000001</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo</t>
+          <t>Cheque en cartera - Municipalidad de Carrilobo</t>
         </is>
       </c>
     </row>
@@ -1950,14 +1700,9 @@
           <t>Disponible</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>ING-000001</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo</t>
+          <t>Cheque en cartera - Municipalidad de Carrilobo</t>
         </is>
       </c>
     </row>
@@ -2015,14 +1760,9 @@
           <t>Disponible</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>ING-000001</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo</t>
+          <t>Cheque en cartera - Municipalidad de Carrilobo</t>
         </is>
       </c>
     </row>
@@ -2080,14 +1820,9 @@
           <t>Disponible</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>ING-000001</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo</t>
+          <t>Cheque en cartera - Municipalidad de Carrilobo</t>
         </is>
       </c>
     </row>
@@ -2102,7 +1837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2229,6 +1964,60 @@
         <is>
           <t>N° cheque</t>
         </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ORD-000001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CASA MARGARIA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>un destornillador</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Cuenta Corriente 30 días</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4665,7 +4454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4745,7 +4534,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -4782,44 +4571,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>USR-000001</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ailen Avalle</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ailen Avalle</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$wagVsgMFwai9CW1o$16a67cee9ae9a25c26a43d75c2fb07af7a8beb682a21454e6f01c80bbf7abdff7e152de3300a56904332e11dda9ba483fbfc7a68661da9d54a35fa7c3991cd48</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Administrador</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>14/10/2026 21:20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4984,6 +4736,43 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CLI-000004</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VS Oncativo SA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>30-70339972-6</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3572695224</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4995,7 +4784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5126,7 +4915,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -5148,7 +4937,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ESCALABILIDAD</t>
+          <t>CARRETON | ESCALABILIDAD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5173,7 +4962,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -5220,7 +5009,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -5267,7 +5056,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -5314,12 +5103,180 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>2027-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UNI-000008</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Camión</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>No posee ITV RTO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SRF504</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FORD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>14.000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UNI-000009</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Semirremolque</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SQB851</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>KRONE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UNI-000011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Camión</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GIZ913</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FORD</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UNI-000012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Semirremolque</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AF770FI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>VULCANO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2027-04-08</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK8"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6174,6 +6131,257 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP-000005</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jonas Gimenez</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>37114897</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20-37114897-4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1993-11-11</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Soltero</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>YAPEYU 1231</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>zona 6</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Oncativo</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3572677448</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AILEN MARIA AVALLE </t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ESPOSA</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>YAPEYU 1231</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ONCATIVO</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3572595387</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Chofer de Camión</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Completa</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Transferencia Bancaria</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>E.1</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP-000006</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AILEN MARIA AVALLE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>40028507</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>27-40028507-7</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1997-02-10</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Soltero</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>YAPEYU 1231</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ZONA 6</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ONCATIVO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3572595387</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ailenavalle1@gmail.com</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Banco Nacion</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ailen Maria Avalle </t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>mente.corazon.vida</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Completa</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Transferencia Bancaria</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>E.1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7510,7 +7718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7611,6 +7819,69 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>Items JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PRE-000001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Servicio</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reparación y Mantenimiento de Maquinaria</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15 días</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Cuenta Corriente</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Presupuesto de servicio</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>[{"id": 1, "tipo": "Servicio", "actividad": "452990 - MANTENIMIENTO Y REPARACI\u00d3N DEL MOTOR N.C.P., MEC\u00c1NICA INTEGRAL", "detalle": "Reparaci\u00f3n y Mantenimiento de Maquinaria", "detalle_trabajo": "Reparaci\u00f3n y Mantenimiento de Maquinaria", "ubicacion": "Municipalidad de Carrilobo", "precio_total": 6000000.0, "total": 6000000.0}]</t>
         </is>
       </c>
     </row>

--- a/operation_data.xlsx
+++ b/operation_data.xlsx
@@ -826,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1015,6 +1015,88 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>00001-00000001</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>30-99922610-4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Reparacion de barredora marca BICUPIRO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1026,7 +1108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1212,6 +1294,88 @@
       <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>00001-00000001</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>30-99922610-4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Reparacion de barredora marca BICUPIRO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
         </is>
       </c>
     </row>
@@ -1580,6 +1744,10 @@
           <t>Disponible</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Cheque en cartera - Municipalidad de Carrilobo</t>
@@ -1640,6 +1808,10 @@
           <t>Disponible</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Cheque en cartera - Municipalidad de Carrilobo</t>
@@ -1700,6 +1872,10 @@
           <t>Disponible</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Cheque en cartera - Municipalidad de Carrilobo</t>
@@ -1760,6 +1936,10 @@
           <t>Disponible</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Cheque en cartera - Municipalidad de Carrilobo</t>
@@ -1820,6 +2000,10 @@
           <t>Disponible</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Cheque en cartera - Municipalidad de Carrilobo</t>
@@ -1982,6 +2166,7 @@
           <t>CASA MARGARIA</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Herramientas</t>
@@ -2016,9 +2201,14 @@
           <t>Pendiente</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>0</v>
       </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2407,11 +2597,15 @@
           <t>Caja Chica</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2452,11 +2646,15 @@
           <t>Efectivo</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2497,11 +2695,15 @@
           <t>Efectivo</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2542,11 +2744,15 @@
           <t>Transferencia - Banco Cordoba</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2587,11 +2793,15 @@
           <t>Transferencia - Banco Cordoba</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4366,12 +4576,14 @@
           <t>Cheques</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Sincronizado automáticamente con Cartera Cheques</t>
@@ -4534,7 +4746,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4783,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4693,6 +4905,8 @@
           <t>Exento / Estado</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Bulnes 727</t>
@@ -4703,6 +4917,7 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4730,11 +4945,15 @@
           <t>Exento / Estado</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4767,11 +4986,54 @@
           <t>3572695224</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CLI-000005</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cooperativa de trabajo UsinaEco Ltda</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33-71631049-9</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>+54 9 2323 58-4820 (Martin)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4908,6 +5170,7 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4923,6 +5186,8 @@
           <t>2027-06-25</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4955,6 +5220,7 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4970,6 +5236,8 @@
           <t>2027-07-08</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5002,6 +5270,7 @@
           <t>2011</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5017,6 +5286,8 @@
           <t>2027-10-21</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5049,6 +5320,7 @@
           <t>2000</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5064,6 +5336,8 @@
           <t>2027-07-08</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5096,6 +5370,7 @@
           <t>2012</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5111,6 +5386,8 @@
           <t>2027-05-05</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5143,6 +5420,7 @@
           <t>14.000</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5153,6 +5431,9 @@
           <t>2027-01-05</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5165,6 +5446,7 @@
           <t>Semirremolque</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>SQB851</t>
@@ -5180,6 +5462,7 @@
           <t>1994</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5195,6 +5478,8 @@
           <t>2027-02-28</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5207,6 +5492,7 @@
           <t>Camión</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>GIZ913</t>
@@ -5222,6 +5508,7 @@
           <t>2007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5237,6 +5524,8 @@
           <t>2027-02-28</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5249,6 +5538,7 @@
           <t>Semirremolque</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>AF770FI</t>
@@ -5264,6 +5554,7 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5279,6 +5570,8 @@
           <t>2027-04-08</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5550,6 +5843,7 @@
           <t>36479383</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>1992-06-11</t>
@@ -5630,6 +5924,7 @@
           <t>PETAK.2026</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>Chofer de Camión</t>
@@ -5640,11 +5935,14 @@
           <t>Completa</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
           <t>Transferencia Bancaria</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
           <t>E.2, B.2</t>
@@ -5680,6 +5978,7 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
@@ -5703,6 +6002,7 @@
           <t>21404440</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>1970-04-24</t>
@@ -5728,6 +6028,7 @@
           <t>Oncativo</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>omarperotti11@gmail.com</t>
@@ -5773,6 +6074,8 @@
           <t>2850400540094100915328</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>Chofer de Camión</t>
@@ -5783,11 +6086,14 @@
           <t>Completa</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
           <t>Transferencia Bancaria</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
           <t>E.1</t>
@@ -5823,6 +6129,7 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
@@ -5846,6 +6153,7 @@
           <t>32889429</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>1987-06-22</t>
@@ -5871,6 +6179,7 @@
           <t>Oncativo</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Longpab22@gmail.com</t>
@@ -5921,6 +6230,7 @@
           <t>PABLOL.2026</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>Chofer de Camión</t>
@@ -5931,11 +6241,14 @@
           <t>Completa</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
           <t>Transferencia Bancaria</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr">
         <is>
           <t>E.1</t>
@@ -5971,6 +6284,7 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
@@ -5994,6 +6308,7 @@
           <t>24242660</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>1974-10-15</t>
@@ -6089,16 +6404,20 @@
           <t>Completa</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
         <is>
           <t>Transferencia Bancaria</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
           <t>E.1</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
           <t>M</t>
@@ -6124,6 +6443,7 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="n">
         <v>1100000</v>
       </c>
@@ -6182,6 +6502,7 @@
           <t>3572677448</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">AILEN MARIA AVALLE </t>
@@ -6207,6 +6528,11 @@
           <t>3572595387</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>Chofer de Camión</t>
@@ -6217,16 +6543,20 @@
           <t>Completa</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr">
         <is>
           <t>Transferencia Bancaria</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr">
         <is>
           <t>E.1</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
           <t>M</t>
@@ -6252,6 +6582,7 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
@@ -6315,6 +6646,11 @@
           <t>ailenavalle1@gmail.com</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>Banco Nacion</t>
@@ -6325,11 +6661,13 @@
           <t xml:space="preserve">Ailen Maria Avalle </t>
         </is>
       </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>mente.corazon.vida</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>Administrativo</t>
@@ -6340,16 +6678,20 @@
           <t>Completa</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr">
         <is>
           <t>Transferencia Bancaria</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr">
         <is>
           <t>E.1</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
           <t>M</t>
@@ -6375,6 +6717,7 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
@@ -6393,7 +6736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6507,9 +6850,24 @@
           <t>Grupo Margaria</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>30-60010614-0</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Combustible</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>+54 9 3572 44-6460</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>GRUPOMARGARIA.SA@GMAIL.COM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6520,11 +6878,14 @@
       <c r="I5" t="n">
         <v>-11050.5</v>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6542,6 +6903,7 @@
           <t>YPF</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Combustible</t>
@@ -6552,6 +6914,7 @@
           <t>3572505350</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -6560,11 +6923,14 @@
       <c r="I6" t="n">
         <v>2304571.93</v>
       </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6582,11 +6948,14 @@
           <t>Shell</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Combustible</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -6595,6 +6964,7 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6605,6 +6975,7 @@
           <t>Saldo inicial pendiente de confirmar</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6637,6 +7008,7 @@
           <t>3572617398</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -6645,11 +7017,13 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>CESOPOL.CORDOBA</t>
@@ -6700,11 +7074,13 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>0000003100008888777766 / YPF.DIRECTO.ONCATIVO</t>
@@ -6742,6 +7118,7 @@
           <t>+54 9 3584 86-6858 (ANAHI)</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -6750,11 +7127,13 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>2850400530094013288211</t>
@@ -6792,6 +7171,7 @@
           <t>+54 9 3572 50-0004</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -6800,11 +7180,13 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>TACHA.BOLDO.POLLO</t>
@@ -6855,6 +7237,7 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6865,6 +7248,7 @@
           <t>Contacto: Alarcon Marina Maricel</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6882,6 +7266,7 @@
           <t>GOMERIA EL ALERO</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Repuestos</t>
@@ -6905,6 +7290,7 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6915,6 +7301,7 @@
           <t>Contacto: Lorena Fernandez</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6947,6 +7334,7 @@
           <t>+54 9 3572 55-0562</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -6955,11 +7343,13 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>cbaceros</t>
@@ -6997,6 +7387,7 @@
           <t>35715322581</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7005,11 +7396,13 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>0200917301000000455283</t>
@@ -7047,6 +7440,7 @@
           <t>3572607034</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7055,11 +7449,14 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7092,6 +7489,7 @@
           <t>3572612848</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7100,11 +7498,13 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>levissamacro</t>
@@ -7142,6 +7542,7 @@
           <t>3572612848</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7150,11 +7551,13 @@
       <c r="I18" t="n">
         <v>0</v>
       </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>lewissrlmacro</t>
@@ -7192,6 +7595,7 @@
           <t>3535107942</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7200,11 +7604,13 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>AMERICAGIS.BN</t>
@@ -7242,6 +7648,7 @@
           <t>3572593304</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7250,11 +7657,13 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>casagonella</t>
@@ -7292,6 +7701,7 @@
           <t>3572509148</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7300,11 +7710,13 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>VENUS.ANCHO.QUESO</t>
@@ -7327,6 +7739,7 @@
           <t>ADMINISTRACION PUMA</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Combustible</t>
@@ -7337,6 +7750,7 @@
           <t>3572446460</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7345,11 +7759,14 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7377,6 +7794,8 @@
           <t>Servicios</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7385,11 +7804,13 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>CCRAVEROZ</t>
@@ -7427,6 +7848,7 @@
           <t>3572677660</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7435,11 +7857,13 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>JALCER.PINTURERIA</t>
@@ -7472,6 +7896,8 @@
           <t>Repuestos</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7480,11 +7906,13 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>DOCTAREP</t>
@@ -7517,6 +7945,12 @@
           <t>Repuestos</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>+54 9 3515 29-5681 (FRANKO)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7525,6 +7959,7 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7538,6 +7973,59 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>2850306430094195849291 / MEDIT.DIESEL.SRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PROV-000024</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Visca Neumaticos S.R.L</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Visca Naumaticos S.R.L</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>30-70753466-0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3572 43-6119 (Emiliano)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Cuenta corriente</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>VISCA.ONCATIVO.RIO</t>
         </is>
       </c>
     </row>
@@ -7825,39 +8313,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PRE-000001</t>
+          <t>PRE-000002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Municipalidad de Carrilobo</t>
+          <t>Cooperativa de trabajo UsinaEco Ltda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30-99901691-6</t>
+          <t>33-71631049-9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Servicio</t>
+          <t>Viaje</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Reparación y Mantenimiento de Maquinaria</t>
+          <t>Unidad Chasis Volkswagen 17.220. Traslado desde Luján hasta Oncativo, tiempo de espera en el lugar, y posterior retorno desde Oncativo hasta Luján.</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6000000</v>
+        <v>4500000</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -7874,14 +8362,15 @@
           <t>Pendiente</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Presupuesto de servicio</t>
+          <t>Pago a 30 días</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>[{"id": 1, "tipo": "Servicio", "actividad": "452990 - MANTENIMIENTO Y REPARACI\u00d3N DEL MOTOR N.C.P., MEC\u00c1NICA INTEGRAL", "detalle": "Reparaci\u00f3n y Mantenimiento de Maquinaria", "detalle_trabajo": "Reparaci\u00f3n y Mantenimiento de Maquinaria", "ubicacion": "Municipalidad de Carrilobo", "precio_total": 6000000.0, "total": 6000000.0}]</t>
+          <t>[{"id": 1, "tipo": "Viaje", "actividad": "492290 - SERVICIO DE TRANSPORTE AUTOMOTOR DE CARGAS N.C.P.", "subtipo_granel": "General", "toneladas": "", "km": "1160", "origen": "Luján, Buenos Aires", "destino": "Oncativo, Córdoba", "descripcion": "Unidad Chasis Volkswagen 17.220. Traslado desde Luján hasta Oncativo, tiempo de espera en el lugar, y posterior retorno desde Oncativo hasta Luján.", "detalle_trabajo": "", "ubicacion": "", "horas": "", "neto": 4500000}]</t>
         </is>
       </c>
     </row>

--- a/operation_data.xlsx
+++ b/operation_data.xlsx
@@ -826,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1053,13 +1053,9 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reparacion de barredora marca BICUPIRO</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>Reparación de barredora marca BICUPIRO</t>
+        </is>
+      </c>
       <c r="M5" t="n">
         <v>6000000</v>
       </c>
@@ -1074,26 +1070,1458 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Cheque Físico (N° 38485564, Bancor): $1,000,000.00 | Cheque Físico (N° 38485565, Bancor): $1,000,000.00 | Cheque Físico (N° 38485566, Bancor): $1,000,000.00 | Cheque Físico (N° 38485567, Bancor): $1,000,000.00 | Cheque Físico (N° 38485568, Bancor): $1,000,000.00 | Cheque Físico (N° 38485569, Bancor): $1,000,000.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>REC-000001</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ING-000002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0000100000002</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reparación Caja Velocidad camión IVECO compactador</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Pendiente de Cobro</t>
         </is>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ING-000003</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>00001-00000003</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>reubicacion tinglado bicicletero terminal</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ING-000004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>00001-00000004</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 22 al 26 de junio</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ING-000005</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>00001-00000005</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 29/06 al 03/07</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ING-000006</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>00001-00000006</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 06 al 10 de julio</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ING-000007</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00001-00000007</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 13 al 17 de julio</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ING-000008</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>00001-00000008</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 20 al 24 de julio</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ING-000009</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>00001-00000009</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 27 al 31 de julio</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ING-000010</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>00001-00000011</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 03 al 07 de Agosto</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ING-000011</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>00001-00000012</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Asociacion deportiva y cultural colazo</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>30-66937993-1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Montaje de luminarias led</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>2420000</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2420000</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>2420000</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Transferencia: $2,420,000.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>REC-000002</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ING-000012</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>00001-00000001</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CAON maquinarias</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>33-71557003-9</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SERVICIO DE GRUA - DESCARGA CABEZAL DRAPER</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N16" t="n">
+        <v>21</v>
+      </c>
+      <c r="O16" t="n">
+        <v>63000</v>
+      </c>
+      <c r="P16" t="n">
+        <v>363000</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Cobrado Parcial</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>322500</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Transferencia: $22,500.00 | E-Cheq (N° 75608272, Macro): $300,000.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>40500</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>REC-000003</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Operación origen: SRV-000001 | Factura creada directamente | Cobro: -9.000,00 RETENCION IMP. A LAS GANACIAS / -31.500 retención IVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ING-000014</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>00001-00000002</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BARTOLOME CERUTTI SRL</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>30-70879590-5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SERVICIO DE GRUA - DESCARGA MINI PALA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>150000</v>
+      </c>
+      <c r="N17" t="n">
+        <v>21</v>
+      </c>
+      <c r="O17" t="n">
+        <v>31500</v>
+      </c>
+      <c r="P17" t="n">
+        <v>181500</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>181500</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Transferencia: $181,500.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>REC-000004</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Operación origen: SRV-000003 | Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ING-000015</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>00001-00000003</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VIAL TRUCK SA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>30-71222595-1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>traslado de equipo de compactador de Oncativo a Rio Segundo y de Rio Segundo a Oncativo.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>700000</v>
+      </c>
+      <c r="N18" t="n">
+        <v>21</v>
+      </c>
+      <c r="O18" t="n">
+        <v>147000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>847000</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>847000</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Operación origen: VIA-000001 | Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ING-000016</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>00001-00000004</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AGROPARTES SA (BLADE)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>30-71048992-7</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>traslado de maquinarias . muestra fico</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Omar Ramon Perotti</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>LFA523</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="N19" t="n">
+        <v>21</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6050000</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>6050000</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Transferencia: $17,687.03 | E-Cheq (N° 36, Santander Rio): $1,999,896.33 | E-Cheq (N° 799, Galicia): $1,713,261.66 | E-Cheq (N° 4799, Galicia): $2,223,634.98 | Retención Ganancias: $95,520.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>REC-000005</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Operación origen: VIA-000002 | Factura creada directamente | Cobro: RETENCION GANACIAS $95.520,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ING-000017</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>00001-00000005</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>LUCIANI RAFAEL (DIEXTRA)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20-24457547-2</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>desmontaje d carteleria</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>150000</v>
+      </c>
+      <c r="N20" t="n">
+        <v>21</v>
+      </c>
+      <c r="O20" t="n">
+        <v>31500</v>
+      </c>
+      <c r="P20" t="n">
+        <v>181500</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>181500</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Operación origen: VIA-000003 | Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ING-000018</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>00001-00000006</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OSCAR POURTAU SA (BRANSEN)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>30-64197643-8</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>traslado de maquinaria - de Oncativo a buenos Aires</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="N21" t="n">
+        <v>21</v>
+      </c>
+      <c r="O21" t="n">
+        <v>735000</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4235000</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Cobrado Parcial</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>4166343.4</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Transferencia: $4,166,343.40 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>68656.60000000001</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>REC-000006</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Operación origen: VIA-000004 | Factura creada directamente | Cobro: RETENCION DE 68.656,60</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ING-000019</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>00001-00000007</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PAOLETTI JUAN MARCELO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>20-27538349-0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TRASLADO DE SEGADORA</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="N22" t="n">
+        <v>21</v>
+      </c>
+      <c r="O22" t="n">
+        <v>336000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1936000</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>1936000</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Transferencia: $1,936,000.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>REC-000007</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ING-000020</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>00001-00000008</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>LA TROJA S.R.L</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>30-70820464-8</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Servicio de Grua</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N23" t="n">
+        <v>21</v>
+      </c>
+      <c r="O23" t="n">
+        <v>315000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1815000</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>1815000</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Transferencia: $1,815,000.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>REC-000008</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Operación origen: SRV-000004 | Factura creada directamente</t>
         </is>
       </c>
     </row>
@@ -1108,7 +2536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1335,13 +2763,9 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reparacion de barredora marca BICUPIRO</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>Reparación de barredora marca BICUPIRO</t>
+        </is>
+      </c>
       <c r="M5" t="n">
         <v>6000000</v>
       </c>
@@ -1356,26 +2780,1458 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Cheque Físico (N° 38485564, Bancor): $1,000,000.00 | Cheque Físico (N° 38485565, Bancor): $1,000,000.00 | Cheque Físico (N° 38485566, Bancor): $1,000,000.00 | Cheque Físico (N° 38485567, Bancor): $1,000,000.00 | Cheque Físico (N° 38485568, Bancor): $1,000,000.00 | Cheque Físico (N° 38485569, Bancor): $1,000,000.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>REC-000001</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ING-000002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0000100000002</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reparación Caja Velocidad camión IVECO compactador</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Pendiente de Cobro</t>
         </is>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ING-000003</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>00001-00000003</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>reubicacion tinglado bicicletero terminal</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ING-000004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>00001-00000004</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 22 al 26 de junio</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ING-000005</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>00001-00000005</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 29/06 al 03/07</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ING-000006</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>00001-00000006</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 06 al 10 de julio</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ING-000007</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00001-00000007</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 13 al 17 de julio</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ING-000008</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>00001-00000008</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 20 al 24 de julio</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ING-000009</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>00001-00000009</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 27 al 31 de julio</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ING-000010</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>00001-00000011</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Municipalidad de Oncativo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>30-99901691-6</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Movimiento de suelo - semana del 03 al 07 de Agosto</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ING-000011</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Factura B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>00001-00000012</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Asociacion deportiva y cultural colazo</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>30-66937993-1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Montaje de luminarias led</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>2420000</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2420000</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>2420000</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Transferencia: $2,420,000.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>REC-000002</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ING-000012</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>00001-00000001</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CAON maquinarias</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>33-71557003-9</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SERVICIO DE GRUA - DESCARGA CABEZAL DRAPER</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N16" t="n">
+        <v>21</v>
+      </c>
+      <c r="O16" t="n">
+        <v>63000</v>
+      </c>
+      <c r="P16" t="n">
+        <v>363000</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Cobrado Parcial</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>322500</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Transferencia: $22,500.00 | E-Cheq (N° 75608272, Macro): $300,000.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>40500</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>REC-000003</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Operación origen: SRV-000001 | Factura creada directamente | Cobro: -9.000,00 RETENCION IMP. A LAS GANACIAS / -31.500 retención IVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ING-000014</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>00001-00000002</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BARTOLOME CERUTTI SRL</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>30-70879590-5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SERVICIO DE GRUA - DESCARGA MINI PALA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>150000</v>
+      </c>
+      <c r="N17" t="n">
+        <v>21</v>
+      </c>
+      <c r="O17" t="n">
+        <v>31500</v>
+      </c>
+      <c r="P17" t="n">
+        <v>181500</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>181500</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Transferencia: $181,500.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>REC-000004</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Operación origen: SRV-000003 | Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ING-000015</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>00001-00000003</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VIAL TRUCK SA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>30-71222595-1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>traslado de equipo de compactador de Oncativo a Rio Segundo y de Rio Segundo a Oncativo.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>700000</v>
+      </c>
+      <c r="N18" t="n">
+        <v>21</v>
+      </c>
+      <c r="O18" t="n">
+        <v>147000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>847000</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>847000</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Operación origen: VIA-000001 | Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ING-000016</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>00001-00000004</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AGROPARTES SA (BLADE)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>30-71048992-7</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>traslado de maquinarias . muestra fico</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Omar Ramon Perotti</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>LFA523</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="N19" t="n">
+        <v>21</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6050000</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>6050000</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Transferencia: $17,687.03 | E-Cheq (N° 36, Santander Rio): $1,999,896.33 | E-Cheq (N° 799, Galicia): $1,713,261.66 | E-Cheq (N° 4799, Galicia): $2,223,634.98 | Retención Ganancias: $95,520.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>REC-000005</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Operación origen: VIA-000002 | Factura creada directamente | Cobro: RETENCION GANACIAS $95.520,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ING-000017</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>00001-00000005</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>LUCIANI RAFAEL (DIEXTRA)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20-24457547-2</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>desmontaje d carteleria</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>150000</v>
+      </c>
+      <c r="N20" t="n">
+        <v>21</v>
+      </c>
+      <c r="O20" t="n">
+        <v>31500</v>
+      </c>
+      <c r="P20" t="n">
+        <v>181500</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Pendiente de Cobro</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>181500</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Operación origen: VIA-000003 | Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ING-000018</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>00001-00000006</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OSCAR POURTAU SA (BRANSEN)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>30-64197643-8</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>traslado de maquinaria - de Oncativo a buenos Aires</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="N21" t="n">
+        <v>21</v>
+      </c>
+      <c r="O21" t="n">
+        <v>735000</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4235000</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Cobrado Parcial</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>4166343.4</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Transferencia: $4,166,343.40 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>68656.60000000001</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>REC-000006</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Operación origen: VIA-000004 | Factura creada directamente | Cobro: RETENCION DE 68.656,60</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ING-000019</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>00001-00000007</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PAOLETTI JUAN MARCELO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>20-27538349-0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TRASLADO DE SEGADORA</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="N22" t="n">
+        <v>21</v>
+      </c>
+      <c r="O22" t="n">
+        <v>336000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1936000</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>1936000</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Transferencia: $1,936,000.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>REC-000007</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Factura creada directamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ING-000020</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Factura A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>00001-00000008</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>LA TROJA S.R.L</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>30-70820464-8</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Servicio de Grua</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N23" t="n">
+        <v>21</v>
+      </c>
+      <c r="O23" t="n">
+        <v>315000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1815000</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>1815000</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Transferencia: $1,815,000.00 - Banco Cordoba</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>REC-000008</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Operación origen: SRV-000004 | Factura creada directamente</t>
         </is>
       </c>
     </row>
@@ -1390,7 +4246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1555,6 +4411,438 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EGR-000001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Proveedor: Visca Neumaticos S.R.L</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CHQ-000001</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>[CHEQUE CHQ-000001] Uso / Endoso de Cheque Físico N° 38485564</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Cheque N° 38485564</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Egreso generado automáticamente al registrar uso del cheque CHQ-000001 (Bancor N° 38485564). Uso / Endoso de Cheque Físico N° 38485564</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EGR-000002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Proveedor: Visca Neumaticos S.R.L</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CHQ-000002</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>[CHEQUE CHQ-000002] Uso / Endoso de Cheque Físico N° 38485565</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Cheque N° 38485565</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Egreso generado automáticamente al registrar uso del cheque CHQ-000002 (Bancor N° 38485565). Uso / Endoso de Cheque Físico N° 38485565</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EGR-000003</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Proveedor: Visca Neumaticos S.R.L</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CHQ-000003</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>[CHEQUE CHQ-000003] Uso / Endoso de Cheque Físico N° 38485566</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Cheque N° 38485566</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Egreso generado automáticamente al registrar uso del cheque CHQ-000003 (Bancor N° 38485566). Uso / Endoso de Cheque Físico N° 38485566</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EGR-000004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Proveedor: Visca Neumaticos S.R.L</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CHQ-000004</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>[CHEQUE CHQ-000004] Uso / Endoso de Cheque Físico N° 38485567</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Cheque N° 38485567</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Egreso generado automáticamente al registrar uso del cheque CHQ-000004 (Bancor N° 38485567). Uso / Endoso de Cheque Físico N° 38485567</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EGR-000005</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Cliente: Lucas Bertaina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CHQ-000005</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>[CHEQUE CHQ-000005] Uso / Endoso de Cheque Físico N° 38485568</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Cheque N° 38485568</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Egreso generado automáticamente al registrar uso del cheque CHQ-000005 (Bancor N° 38485568). Uso / Endoso de Cheque Físico N° 38485568</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EGR-000006</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cliente: Lucas Bertaina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CHQ-000006</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>[CHEQUE CHQ-000006] Uso / Endoso de Cheque Físico N° 38485569</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Cheque N° 38485569</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Egreso generado automáticamente al registrar uso del cheque CHQ-000006 (Bancor N° 38485569). Uso / Endoso de Cheque Físico N° 38485569</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1566,7 +4854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1698,7 +4986,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1716,7 +5004,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-99901691-6</t>
+          <t>30-99922610-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1736,21 +5024,37 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ECONCATIVO S.A.S.</t>
+          <t>Proveedor: Visca Neumaticos S.R.L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>Usado</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Proveedor: Visca Neumaticos S.R.L</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>EGR-000001</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Cheque en cartera - Municipalidad de Carrilobo</t>
+          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo | Uso / Endoso de Cheque Físico N° 38485564</t>
         </is>
       </c>
     </row>
@@ -1762,7 +5066,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1780,7 +5084,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-99901691-6</t>
+          <t>30-99922610-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1800,21 +5104,37 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ECONCATIVO S.A.S.</t>
+          <t>Proveedor: Visca Neumaticos S.R.L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>Usado</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Proveedor: Visca Neumaticos S.R.L</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>EGR-000002</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Cheque en cartera - Municipalidad de Carrilobo</t>
+          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo | Uso / Endoso de Cheque Físico N° 38485565</t>
         </is>
       </c>
     </row>
@@ -1826,7 +5146,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1844,7 +5164,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-99901691-6</t>
+          <t>30-99922610-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1859,26 +5179,42 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ECONCATIVO S.A.S.</t>
+          <t>Proveedor: Visca Neumaticos S.R.L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>Usado</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Proveedor: Visca Neumaticos S.R.L</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>EGR-000003</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Cheque en cartera - Municipalidad de Carrilobo</t>
+          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo | Uso / Endoso de Cheque Físico N° 38485566 | Uso / Endoso de Cheque Físico N° 38485566</t>
         </is>
       </c>
     </row>
@@ -1890,7 +5226,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1908,7 +5244,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-99901691-6</t>
+          <t>30-99922610-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1918,31 +5254,47 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>38485568</t>
+          <t>38485567</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ECONCATIVO S.A.S.</t>
+          <t>Proveedor: Visca Neumaticos S.R.L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+          <t>Usado</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Proveedor: Visca Neumaticos S.R.L</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>EGR-000004</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Cheque en cartera - Municipalidad de Carrilobo</t>
+          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo | Uso / Endoso de Cheque Físico N° 38485567</t>
         </is>
       </c>
     </row>
@@ -1954,7 +5306,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1972,7 +5324,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30-99901691-6</t>
+          <t>30-99922610-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1987,26 +5339,382 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2027-03-12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>Cliente: Lucas Bertaina</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Usado</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Cliente: Lucas Bertaina</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>EGR-000005</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo | Uso / Endoso de Cheque Físico N° 38485568</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CHQ-000006</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cheque Físico</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Municipalidad de Carrilobo</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>30-99922610-4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bancor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>38485569</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2027-04-12</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Cliente: Lucas Bertaina</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Usado</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Cliente: Lucas Bertaina</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>EGR-000006</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ING-000001</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Cobro de Ingreso ING-000001 - Municipalidad de Carrilobo | Uso / Endoso de Cheque Físico N° 38485569</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CHQ-000007</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>E-Cheq</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CAON maquinarias</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>33-71557003-9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>75608272</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>ECONCATIVO S.A.S.</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Disponible</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Cheque en cartera - Municipalidad de Carrilobo</t>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ING-000012</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Cobro de Ingreso ING-000012 - CAON maquinarias</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CHQ-000008</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>E-Cheq</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1999896.33</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AGROPARTES SA (BLADE)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>30-71048992-7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Santander Rio</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ECONCATIVO S.A.S.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ING-000016</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Cobro de Ingreso ING-000016 - AGROPARTES SA (BLADE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CHQ-000009</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>E-Cheq</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1713261.66</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AGROPARTES SA (BLADE)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>30-71048992-7</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ECONCATIVO S.A.S.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ING-000016</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Cobro de Ingreso ING-000016 - AGROPARTES SA (BLADE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CHQ-000010</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>E-Cheq</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2223634.98</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AGROPARTES SA (BLADE)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>30-71048992-7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4799</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ECONCATIVO S.A.S.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ING-000016</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Cobro de Ingreso ING-000016 - AGROPARTES SA (BLADE)</t>
         </is>
       </c>
     </row>
@@ -2166,7 +5874,6 @@
           <t>CASA MARGARIA</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Herramientas</t>
@@ -2201,14 +5908,9 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2597,15 +6299,11 @@
           <t>Caja Chica</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2646,15 +6344,11 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2695,15 +6389,11 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2744,15 +6434,11 @@
           <t>Transferencia - Banco Cordoba</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2793,15 +6479,11 @@
           <t>Transferencia - Banco Cordoba</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4576,14 +8258,12 @@
           <t>Cheques</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Sincronizado automáticamente con Cartera Cheques</t>
@@ -4666,7 +8346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4783,7 +8463,44 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>USR-000001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ailen Avalle</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ailen Avalle</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$i0tSGrWCj6zxibi5$648097bd1cbf3cb5098c69e38c5f851b4023504b987773ad9b6bc719c5e6a1f1304658be872f38eadaad876591bd30336c1d27a92c149d5756975f8f485288f9</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>22/10/2026 09:56</t>
         </is>
       </c>
     </row>
@@ -4798,7 +8515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4905,8 +8622,6 @@
           <t>Exento / Estado</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Bulnes 727</t>
@@ -4917,7 +8632,6 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4945,15 +8659,11 @@
           <t>Exento / Estado</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4986,14 +8696,11 @@
           <t>3572695224</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5026,14 +8733,506 @@
           <t>+54 9 2323 58-4820 (Martin)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CLI-000006</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lucas Bertaina</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20-36479334-1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Particular</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3572613335</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CLI-000007</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Asociacion deportiva y cultural colazo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>30-66937993-1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Exento / Estado</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3532400333</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CLI-000008</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CAON maquinarias</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>33-71557003-9</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3572536495</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CLI-000009</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BARTOLOME CERUTTI SRL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>30-70879590-5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CLI-000010</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VIAL TRUCK SA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>30-71222595-1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CLI-000011</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AGROPARTES SA (BLADE)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>30-71048992-7</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CLI-000012</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LUCIANI RAFAEL (DIEXTRA)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20-24457547-2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Particular</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CLI-000013</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>OSCAR POURTAU SA (BRANSEN)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>30-64197643-8</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CLI-000014</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PAOLETTI JUAN MARCELO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>20-27538349-0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CLI-000015</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LA TROJA S.R.L</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>30-70820464-8</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CLI-000016</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BONO, NESTOR FABIAN Y BONO, MAXIMILIANO FABIAN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>30-71513224-5</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CLI-000017</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CLE-SIR S.A</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>30-71837334-0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CLI-000018</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ASOCIACION DE COOPERATIVAS ARGENTINAS - COOP LTDA.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>30-50012088-2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CLI-000019</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A &amp; A TRILLINI S.A.S</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>30-71826282-4</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CLI-000020</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MURATURE ONCATIVO S.A.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>30-71140666-9</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Responsable Inscripto</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5170,7 +9369,6 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5186,8 +9384,6 @@
           <t>2027-06-25</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5220,7 +9416,6 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5236,8 +9431,6 @@
           <t>2027-07-08</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5270,7 +9463,6 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5286,8 +9478,6 @@
           <t>2027-10-21</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5320,7 +9510,6 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5336,8 +9525,6 @@
           <t>2027-07-08</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5370,7 +9557,6 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5386,8 +9572,6 @@
           <t>2027-05-05</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5420,7 +9604,6 @@
           <t>14.000</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5431,9 +9614,6 @@
           <t>2027-01-05</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5446,7 +9626,6 @@
           <t>Semirremolque</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>SQB851</t>
@@ -5462,7 +9641,6 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5478,8 +9656,6 @@
           <t>2027-02-28</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5492,7 +9668,6 @@
           <t>Camión</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>GIZ913</t>
@@ -5508,7 +9683,6 @@
           <t>2007</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5524,8 +9698,6 @@
           <t>2027-02-28</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5538,7 +9710,6 @@
           <t>Semirremolque</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>AF770FI</t>
@@ -5554,7 +9725,6 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5570,8 +9740,6 @@
           <t>2027-04-08</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5584,7 +9752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK10"/>
+  <dimension ref="A1:AK11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5843,7 +10011,6 @@
           <t>36479383</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>1992-06-11</t>
@@ -5924,7 +10091,6 @@
           <t>PETAK.2026</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>Chofer de Camión</t>
@@ -5935,14 +10101,11 @@
           <t>Completa</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
           <t>Transferencia Bancaria</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
           <t>E.2, B.2</t>
@@ -5978,7 +10141,6 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
@@ -6002,7 +10164,6 @@
           <t>21404440</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>1970-04-24</t>
@@ -6028,7 +10189,6 @@
           <t>Oncativo</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>omarperotti11@gmail.com</t>
@@ -6074,8 +10234,6 @@
           <t>2850400540094100915328</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>Chofer de Camión</t>
@@ -6086,14 +10244,11 @@
           <t>Completa</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
           <t>Transferencia Bancaria</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
           <t>E.1</t>
@@ -6129,7 +10284,6 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
@@ -6153,7 +10307,6 @@
           <t>32889429</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>1987-06-22</t>
@@ -6179,7 +10332,6 @@
           <t>Oncativo</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Longpab22@gmail.com</t>
@@ -6230,7 +10382,6 @@
           <t>PABLOL.2026</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>Chofer de Camión</t>
@@ -6241,14 +10392,11 @@
           <t>Completa</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
           <t>Transferencia Bancaria</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr">
         <is>
           <t>E.1</t>
@@ -6284,7 +10432,6 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
@@ -6308,7 +10455,6 @@
           <t>24242660</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>1974-10-15</t>
@@ -6404,20 +10550,16 @@
           <t>Completa</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
         <is>
           <t>Transferencia Bancaria</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
           <t>E.1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
           <t>M</t>
@@ -6443,7 +10585,6 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="n">
         <v>1100000</v>
       </c>
@@ -6502,7 +10643,6 @@
           <t>3572677448</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">AILEN MARIA AVALLE </t>
@@ -6528,11 +10668,6 @@
           <t>3572595387</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>Chofer de Camión</t>
@@ -6543,20 +10678,16 @@
           <t>Completa</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr">
         <is>
           <t>Transferencia Bancaria</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr">
         <is>
           <t>E.1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
           <t>M</t>
@@ -6582,7 +10713,6 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
@@ -6646,11 +10776,6 @@
           <t>ailenavalle1@gmail.com</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>Banco Nacion</t>
@@ -6661,13 +10786,11 @@
           <t xml:space="preserve">Ailen Maria Avalle </t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>mente.corazon.vida</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>Administrativo</t>
@@ -6678,20 +10801,16 @@
           <t>Completa</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr">
         <is>
           <t>Transferencia Bancaria</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr">
         <is>
           <t>E.1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
           <t>M</t>
@@ -6717,11 +10836,108 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP-000007</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>29466684</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20-29466684-3</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Soltero</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>RUTA 9 KM 627</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3572547554</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>lmvschetto@gmail.comn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Chofer de Camión</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Completa</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Transferencia Bancaria</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>E.1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6878,14 +11094,11 @@
       <c r="I5" t="n">
         <v>-11050.5</v>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6903,7 +11116,6 @@
           <t>YPF</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Combustible</t>
@@ -6914,7 +11126,6 @@
           <t>3572505350</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -6923,14 +11134,11 @@
       <c r="I6" t="n">
         <v>2304571.93</v>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6948,14 +11156,11 @@
           <t>Shell</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Combustible</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -6964,7 +11169,6 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6975,7 +11179,6 @@
           <t>Saldo inicial pendiente de confirmar</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7008,7 +11211,6 @@
           <t>3572617398</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7017,13 +11219,11 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>CESOPOL.CORDOBA</t>
@@ -7074,13 +11274,11 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>0000003100008888777766 / YPF.DIRECTO.ONCATIVO</t>
@@ -7118,7 +11316,6 @@
           <t>+54 9 3584 86-6858 (ANAHI)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7127,13 +11324,11 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>2850400530094013288211</t>
@@ -7171,7 +11366,6 @@
           <t>+54 9 3572 50-0004</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7180,13 +11374,11 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>TACHA.BOLDO.POLLO</t>
@@ -7237,7 +11429,6 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7248,7 +11439,6 @@
           <t>Contacto: Alarcon Marina Maricel</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7266,7 +11456,6 @@
           <t>GOMERIA EL ALERO</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Repuestos</t>
@@ -7290,7 +11479,6 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7301,7 +11489,6 @@
           <t>Contacto: Lorena Fernandez</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7334,7 +11521,6 @@
           <t>+54 9 3572 55-0562</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7343,13 +11529,11 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>cbaceros</t>
@@ -7387,7 +11571,6 @@
           <t>35715322581</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7396,13 +11579,11 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>0200917301000000455283</t>
@@ -7440,7 +11621,6 @@
           <t>3572607034</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7449,14 +11629,11 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7489,7 +11666,6 @@
           <t>3572612848</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7498,13 +11674,11 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>levissamacro</t>
@@ -7542,7 +11716,6 @@
           <t>3572612848</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7551,13 +11724,11 @@
       <c r="I18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>lewissrlmacro</t>
@@ -7595,7 +11766,6 @@
           <t>3535107942</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7604,13 +11774,11 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>AMERICAGIS.BN</t>
@@ -7648,7 +11816,6 @@
           <t>3572593304</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7657,13 +11824,11 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>casagonella</t>
@@ -7701,7 +11866,6 @@
           <t>3572509148</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7710,13 +11874,11 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>VENUS.ANCHO.QUESO</t>
@@ -7739,7 +11901,6 @@
           <t>ADMINISTRACION PUMA</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Combustible</t>
@@ -7750,7 +11911,6 @@
           <t>3572446460</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7759,14 +11919,11 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7794,8 +11951,6 @@
           <t>Servicios</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7804,13 +11959,11 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>CCRAVEROZ</t>
@@ -7848,7 +12001,6 @@
           <t>3572677660</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7857,13 +12009,11 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>JALCER.PINTURERIA</t>
@@ -7896,8 +12046,6 @@
           <t>Repuestos</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7906,13 +12054,11 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>DOCTAREP</t>
@@ -7950,7 +12096,6 @@
           <t>+54 9 3515 29-5681 (FRANKO)</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -7959,7 +12104,6 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8007,7 +12151,6 @@
           <t>3572 43-6119 (Emiliano)</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Cuenta corriente</t>
@@ -8016,13 +12159,11 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>VISCA.ONCATIVO.RIO</t>
@@ -8362,7 +12503,6 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Pago a 30 días</t>
@@ -8385,7 +12525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8544,6 +12684,559 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SRV-000001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CAON maquinarias</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SERVICIO DE GRUA - DESCARGA CABEZAL DRAPER</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SERVICIO DE GRUA - DESCARGA CABEZAL DRAPER</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Facturado</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>ING-000012</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Factura vinculada: 00001-00000001 (ING-000012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SRV-000003</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>BARTOLOME CERUTTI SRL</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SERVICIO DE GRUA - DESCARGA MINI PALA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SERVICIO DE GRUA - DESCARGA MINI PALA</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Facturado</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>ING-000014</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Factura vinculada: 00001-00000002 (ING-000014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SRV-000004</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>LA TROJA S.R.L</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Servicio de Grua</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Servicio de Grua</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Facturado</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>ING-000020</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Factura vinculada: 00001-00000008 (ING-000020)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VIA-000001</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>VIAL TRUCK SA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>traslado de equipo de compactador de Oncativo a Rio Segundo y de Rio Segundo a Oncativo.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>traslado de equipo de compactador de Oncativo a Rio Segundo y de Rio Segundo a Oncativo.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>700000</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Facturado</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>ING-000015</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Factura vinculada: 00001-00000003 (ING-000015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VIA-000002</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Omar Ramon Perotti</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LFA523</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AGROPARTES SA (BLADE)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>traslado de maquinarias . muestra fico</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>traslado de maquinarias . muestra fico</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Facturado</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>ING-000016</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Factura vinculada: 00001-00000004 (ING-000016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VIA-000003</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MARIANO LEOPOLDO VASCHETTO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>JUH164</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>LUCIANI RAFAEL (DIEXTRA)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>desmontaje d carteleria</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>desmontaje d carteleria</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>150000</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Facturado</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>ING-000017</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Factura vinculada: 00001-00000005 (ING-000017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VIA-000004</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>POR ASIGNAR</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>POR ASIGNAR</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>POR DEFINIR</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>OSCAR POURTAU SA (BRANSEN)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>traslado de maquinaria - de Oncativo a buenos Aires</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>traslado de maquinaria - de Oncativo a buenos Aires</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Facturado</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>ING-000018</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Factura vinculada: 00001-00000006 (ING-000018)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
